--- a/(枠)◯年度一式/項目別手数料歳入.xlsx
+++ b/(枠)◯年度一式/項目別手数料歳入.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6273F4FF-DF2E-4BFF-93D6-1DF01D6445F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE35A8AE-95B9-464C-90D2-4E381D99B860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="19395" windowHeight="15480" xr2:uid="{069F358C-EF73-42D0-BED5-2ED39B921C1F}"/>
+    <workbookView xWindow="2490" yWindow="330" windowWidth="20010" windowHeight="15480" xr2:uid="{069F358C-EF73-42D0-BED5-2ED39B921C1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>大</t>
     <rPh sb="0" eb="1">
@@ -202,81 +203,6 @@
   </si>
   <si>
     <t>エアコン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平成30年度  粗大ごみ処理手数料</t>
-    <rPh sb="0" eb="2">
-      <t>ヘイセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ソダイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>テスウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平成30年度  あわせ処理産業廃棄物処理手数料</t>
-    <rPh sb="0" eb="2">
-      <t>ヘイセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サンギョウ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ハイキブツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>テスウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平成30年度  家電リサイクル収集運搬手数料</t>
-    <rPh sb="0" eb="2">
-      <t>ヘイセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カデン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シュウシュウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ウンパン</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>テスウリョウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -492,22 +418,10 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -517,6 +431,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -19490,6 +19416,50 @@
         </row>
       </sheetData>
       <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19793,13 +19763,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="A1" s="20" t="str">
+        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  粗大ごみ処理手数料"</f>
+        <v>令和9年度  粗大ごみ処理手数料</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -20033,22 +20004,22 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="19"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="16" t="s">
@@ -20299,13 +20270,14 @@
       <c r="P11" s="9"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
+      <c r="A12" s="20" t="str">
+        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  あわせ処理産業廃棄物処理手数料"</f>
+        <v>令和9年度  あわせ処理産業廃棄物処理手数料</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
       <c r="M12" s="9"/>
       <c r="P12" s="9"/>
     </row>
@@ -20541,22 +20513,22 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="19"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="23"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="16" t="s">
@@ -20806,13 +20778,14 @@
       <c r="M22" s="9"/>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="A23" s="20" t="str">
+        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  家電リサイクル収集運搬手数料"</f>
+        <v>令和9年度  家電リサイクル収集運搬手数料</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
       <c r="M23" s="9"/>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -20862,7 +20835,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -20961,7 +20934,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="22"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="4" t="s">
         <v>23</v>
       </c>
@@ -21058,7 +21031,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="22"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="4" t="s">
         <v>27</v>
       </c>
@@ -21155,7 +21128,7 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="22"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
@@ -21252,7 +21225,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="22"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="4" t="s">
         <v>25</v>
       </c>
@@ -21349,7 +21322,7 @@
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="20"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="4" t="s">
         <v>28</v>
       </c>
@@ -21446,22 +21419,22 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="17"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="19"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="23"/>
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="16" t="s">
@@ -21832,11 +21805,11 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="10">
         <f>SUM(D32:D37)</f>
         <v>0</v>
@@ -21891,11 +21864,11 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="13" t="str">
         <f>IF(SUM(D10,D21,D38)=0,"",SUM(D10,D21,D38))</f>
         <v/>
@@ -21951,6 +21924,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A7:A9"/>
@@ -21962,14 +21943,6 @@
     <mergeCell ref="A25:A30"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="A31:P31"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>

--- a/(枠)◯年度一式/項目別手数料歳入.xlsx
+++ b/(枠)◯年度一式/項目別手数料歳入.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE35A8AE-95B9-464C-90D2-4E381D99B860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F317EA-4F57-4DAE-B310-C357DAFB0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="330" windowWidth="20010" windowHeight="15480" xr2:uid="{069F358C-EF73-42D0-BED5-2ED39B921C1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{069F358C-EF73-42D0-BED5-2ED39B921C1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,10 +418,22 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -431,18 +443,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -469,6 +469,50 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="調定04"/>
       <sheetName val="調定05"/>
       <sheetName val="調定06"/>
@@ -13656,7 +13700,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -18412,7 +18456,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -19416,50 +19460,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="A-1"/>
-      <sheetName val="A-2"/>
-      <sheetName val="B-1"/>
-      <sheetName val="収集（全般）"/>
-      <sheetName val="可燃"/>
-      <sheetName val="不燃・木くず・海岸清掃"/>
-      <sheetName val="ビン類"/>
-      <sheetName val="缶類"/>
-      <sheetName val="ペットボトル"/>
-      <sheetName val="紙類"/>
-      <sheetName val="粗大"/>
-      <sheetName val="産廃水産・医療・汚泥"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="9">
-          <cell r="E9">
-            <v>2027</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19763,14 +19763,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
-        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  粗大ごみ処理手数料"</f>
+      <c r="A1" s="15" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度  粗大ごみ処理手数料"</f>
         <v>令和9年度  粗大ごみ処理手数料</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -19829,51 +19829,51 @@
         <v>1000</v>
       </c>
       <c r="D3" s="6">
-        <f>SUM([1]調定04!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定04!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="E3" s="6">
-        <f>SUM([1]調定05!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定05!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="F3" s="6">
-        <f>SUM([1]調定06!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定06!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="G3" s="6">
-        <f>SUM([1]調定07!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定07!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="H3" s="6">
-        <f>SUM([1]調定08!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定08!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>SUM([1]調定09!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定09!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="J3" s="6">
-        <f>SUM([1]調定10!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定10!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="K3" s="6">
-        <f>SUM([1]調定11!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定11!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="L3" s="6">
-        <f>SUM([1]調定12!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定12!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="M3" s="6">
-        <f>SUM([1]調定01!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定01!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="N3" s="6">
-        <f>SUM([1]調定02!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定02!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="O3" s="6">
-        <f>SUM([1]調定03!$G$4:$G$999)/$C$3</f>
+        <f>SUM([2]調定03!$G$4:$G$999)/$C$3</f>
         <v>0</v>
       </c>
       <c r="P3" s="6">
@@ -19890,51 +19890,51 @@
         <v>800</v>
       </c>
       <c r="D4" s="6">
-        <f>SUM([1]調定04!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定04!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="E4" s="6">
-        <f>SUM([1]調定05!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定05!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="F4" s="6">
-        <f>SUM([1]調定06!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定06!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="G4" s="6">
-        <f>SUM([1]調定07!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定07!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="H4" s="6">
-        <f>SUM([1]調定08!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定08!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>SUM([1]調定09!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定09!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="J4" s="6">
-        <f>SUM([1]調定10!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定10!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="K4" s="6">
-        <f>SUM([1]調定11!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定11!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="L4" s="6">
-        <f>SUM([1]調定12!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定12!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="M4" s="6">
-        <f>SUM([1]調定01!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定01!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="N4" s="6">
-        <f>SUM([1]調定02!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定02!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="O4" s="6">
-        <f>SUM([1]調定03!$F$4:$F$999)/$C$4</f>
+        <f>SUM([2]調定03!$F$4:$F$999)/$C$4</f>
         <v>0</v>
       </c>
       <c r="P4" s="6">
@@ -19951,51 +19951,51 @@
         <v>500</v>
       </c>
       <c r="D5" s="6">
-        <f>SUM([1]調定04!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定04!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="E5" s="6">
-        <f>SUM([1]調定05!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定05!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="F5" s="6">
-        <f>SUM([1]調定06!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定06!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <f>SUM([1]調定07!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定07!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <f>SUM([1]調定08!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定08!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="I5" s="6">
-        <f>SUM([1]調定09!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定09!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="J5" s="6">
-        <f>SUM([1]調定10!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定10!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="K5" s="6">
-        <f>SUM([1]調定11!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定11!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="L5" s="6">
-        <f>SUM([1]調定12!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定12!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="M5" s="6">
-        <f>SUM([1]調定01!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定01!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="N5" s="6">
-        <f>SUM([1]調定02!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定02!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="O5" s="6">
-        <f>SUM([1]調定03!$E$4:$E$999)/$C$5</f>
+        <f>SUM([2]調定03!$E$4:$E$999)/$C$5</f>
         <v>0</v>
       </c>
       <c r="P5" s="6">
@@ -20004,22 +20004,22 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="23"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="19"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="16" t="s">
@@ -20270,14 +20270,14 @@
       <c r="P11" s="9"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="20" t="str">
-        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  あわせ処理産業廃棄物処理手数料"</f>
+      <c r="A12" s="15" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度  あわせ処理産業廃棄物処理手数料"</f>
         <v>令和9年度  あわせ処理産業廃棄物処理手数料</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
       <c r="M12" s="9"/>
       <c r="P12" s="9"/>
     </row>
@@ -20338,51 +20338,51 @@
         <v>10</v>
       </c>
       <c r="D14" s="6">
-        <f>COUNT([2]調定04!$E$1:$E$999)</f>
+        <f>COUNT([3]調定04!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="E14" s="6">
-        <f>COUNT([2]調定05!$E$1:$E$999)</f>
+        <f>COUNT([3]調定05!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="F14" s="6">
-        <f>COUNT([2]調定06!$E$1:$E$999)</f>
+        <f>COUNT([3]調定06!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="G14" s="6">
-        <f>COUNT([2]調定07!$E$1:$E$999)</f>
+        <f>COUNT([3]調定07!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="H14" s="6">
-        <f>COUNT([2]調定08!$E$1:$E$999)</f>
+        <f>COUNT([3]調定08!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="I14" s="6">
-        <f>COUNT([2]調定09!$E$1:$E$999)</f>
+        <f>COUNT([3]調定09!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="J14" s="6">
-        <f>COUNT([2]調定10!$E$1:$E$999)</f>
+        <f>COUNT([3]調定10!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="K14" s="6">
-        <f>COUNT([2]調定11!$E$1:$E$999)</f>
+        <f>COUNT([3]調定11!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="L14" s="6">
-        <f>COUNT([2]調定12!$E$1:$E$999)</f>
+        <f>COUNT([3]調定12!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="M14" s="6">
-        <f>COUNT([2]調定01!$E$1:$E$999)</f>
+        <f>COUNT([3]調定01!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <f>COUNT([2]調定02!$E$1:$E$999)</f>
+        <f>COUNT([3]調定02!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="O14" s="6">
-        <f>COUNT([2]調定03!$E$1:$E$999)</f>
+        <f>COUNT([3]調定03!$E$1:$E$999)</f>
         <v>0</v>
       </c>
       <c r="P14" s="6">
@@ -20399,51 +20399,51 @@
         <v>10</v>
       </c>
       <c r="D15" s="6">
-        <f>COUNT([2]調定04!$F$1:$F$999)</f>
+        <f>COUNT([3]調定04!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="E15" s="6">
-        <f>COUNT([2]調定05!$F$1:$F$999)</f>
+        <f>COUNT([3]調定05!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="F15" s="6">
-        <f>COUNT([2]調定06!$F$1:$F$999)</f>
+        <f>COUNT([3]調定06!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <f>COUNT([2]調定07!$F$1:$F$999)</f>
+        <f>COUNT([3]調定07!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="H15" s="6">
-        <f>COUNT([2]調定08!$F$1:$F$999)</f>
+        <f>COUNT([3]調定08!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="I15" s="6">
-        <f>COUNT([2]調定09!$F$1:$F$999)</f>
+        <f>COUNT([3]調定09!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="J15" s="6">
-        <f>COUNT([2]調定10!$F$1:$F$999)</f>
+        <f>COUNT([3]調定10!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="K15" s="6">
-        <f>COUNT([2]調定11!$F$1:$F$999)</f>
+        <f>COUNT([3]調定11!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="L15" s="6">
-        <f>COUNT([2]調定12!$F$1:$F$999)</f>
+        <f>COUNT([3]調定12!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="M15" s="6">
-        <f>COUNT([2]調定01!$F$1:$F$999)</f>
+        <f>COUNT([3]調定01!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="N15" s="6">
-        <f>COUNT([2]調定02!$F$1:$F$999)</f>
+        <f>COUNT([3]調定02!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <f>COUNT([2]調定03!$F$1:$F$999)</f>
+        <f>COUNT([3]調定03!$F$1:$F$999)</f>
         <v>0</v>
       </c>
       <c r="P15" s="6">
@@ -20460,51 +20460,51 @@
         <v>10</v>
       </c>
       <c r="D16" s="6">
-        <f>COUNT([2]調定04!$G$1:$G$999)</f>
+        <f>COUNT([3]調定04!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="E16" s="6">
-        <f>COUNT([2]調定05!$G$1:$G$999)</f>
+        <f>COUNT([3]調定05!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="F16" s="6">
-        <f>COUNT([2]調定06!$G$1:$G$999)</f>
+        <f>COUNT([3]調定06!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>COUNT([2]調定07!$G$1:$G$999)</f>
+        <f>COUNT([3]調定07!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="H16" s="6">
-        <f>COUNT([2]調定08!$G$1:$G$999)</f>
+        <f>COUNT([3]調定08!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="I16" s="6">
-        <f>COUNT([2]調定09!$G$1:$G$999)</f>
+        <f>COUNT([3]調定09!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="J16" s="6">
-        <f>COUNT([2]調定10!$G$1:$G$999)</f>
+        <f>COUNT([3]調定10!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="K16" s="6">
-        <f>COUNT([2]調定11!$G$1:$G$999)</f>
+        <f>COUNT([3]調定11!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="L16" s="6">
-        <f>COUNT([2]調定12!$G$1:$G$999)</f>
+        <f>COUNT([3]調定12!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="M16" s="6">
-        <f>COUNT([2]調定01!$G$1:$G$999)</f>
+        <f>COUNT([3]調定01!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="N16" s="6">
-        <f>COUNT([2]調定02!$G$1:$G$999)</f>
+        <f>COUNT([3]調定02!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="O16" s="6">
-        <f>COUNT([2]調定03!$G$1:$G$999)</f>
+        <f>COUNT([3]調定03!$G$1:$G$999)</f>
         <v>0</v>
       </c>
       <c r="P16" s="6">
@@ -20513,22 +20513,22 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="23"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="19"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="16" t="s">
@@ -20541,51 +20541,51 @@
         <v>10</v>
       </c>
       <c r="D18" s="6">
-        <f>SUM([2]調定04!$E$4:$E$999)</f>
+        <f>SUM([3]調定04!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="E18" s="6">
-        <f>SUM([2]調定05!$E$4:$E$999)</f>
+        <f>SUM([3]調定05!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="F18" s="6">
-        <f>SUM([2]調定06!$E$4:$E$999)</f>
+        <f>SUM([3]調定06!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <f>SUM([2]調定07!$E$4:$E$999)</f>
+        <f>SUM([3]調定07!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="H18" s="6">
-        <f>SUM([2]調定08!$E$4:$E$999)</f>
+        <f>SUM([3]調定08!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="I18" s="6">
-        <f>SUM([2]調定09!$E$4:$E$999)</f>
+        <f>SUM([3]調定09!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="J18" s="6">
-        <f>SUM([2]調定10!$E$4:$E$999)</f>
+        <f>SUM([3]調定10!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="K18" s="6">
-        <f>SUM([2]調定11!$E$4:$E$999)</f>
+        <f>SUM([3]調定11!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="L18" s="6">
-        <f>SUM([2]調定12!$E$4:$E$999)</f>
+        <f>SUM([3]調定12!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="M18" s="6">
-        <f>SUM([2]調定01!$E$4:$E$999)</f>
+        <f>SUM([3]調定01!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="N18" s="6">
-        <f>SUM([2]調定02!$E$4:$E$999)</f>
+        <f>SUM([3]調定02!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="O18" s="6">
-        <f>SUM([2]調定03!$E$4:$E$999)</f>
+        <f>SUM([3]調定03!$E$4:$E$999)</f>
         <v>0</v>
       </c>
       <c r="P18" s="6">
@@ -20602,51 +20602,51 @@
         <v>10</v>
       </c>
       <c r="D19" s="6">
-        <f>SUM([2]調定04!$F$4:$F$999)</f>
+        <f>SUM([3]調定04!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="E19" s="6">
-        <f>SUM([2]調定05!$F$4:$F$999)</f>
+        <f>SUM([3]調定05!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="F19" s="6">
-        <f>SUM([2]調定06!$F$4:$F$999)</f>
+        <f>SUM([3]調定06!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="G19" s="6">
-        <f>SUM([2]調定07!$F$4:$F$999)</f>
+        <f>SUM([3]調定07!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="H19" s="6">
-        <f>SUM([2]調定08!$F$4:$F$999)</f>
+        <f>SUM([3]調定08!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="I19" s="6">
-        <f>SUM([2]調定09!$F$4:$F$999)</f>
+        <f>SUM([3]調定09!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="J19" s="6">
-        <f>SUM([2]調定10!$F$4:$F$999)</f>
+        <f>SUM([3]調定10!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="K19" s="6">
-        <f>SUM([2]調定11!$F$4:$F$999)</f>
+        <f>SUM([3]調定11!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="L19" s="6">
-        <f>SUM([2]調定12!$F$4:$F$999)</f>
+        <f>SUM([3]調定12!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="M19" s="6">
-        <f>SUM([2]調定01!$F$4:$F$999)</f>
+        <f>SUM([3]調定01!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="N19" s="6">
-        <f>SUM([2]調定02!$F$4:$F$999)</f>
+        <f>SUM([3]調定02!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="O19" s="6">
-        <f>SUM([2]調定03!$F$4:$F$999)</f>
+        <f>SUM([3]調定03!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="P19" s="6">
@@ -20663,51 +20663,51 @@
         <v>10</v>
       </c>
       <c r="D20" s="6">
-        <f>SUM([2]調定04!$G$4:$G$999)</f>
+        <f>SUM([3]調定04!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="E20" s="6">
-        <f>SUM([2]調定05!$G$4:$G$999)</f>
+        <f>SUM([3]調定05!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="F20" s="6">
-        <f>SUM([2]調定06!$G$4:$G$999)</f>
+        <f>SUM([3]調定06!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="G20" s="6">
-        <f>SUM([2]調定07!$G$4:$G$999)</f>
+        <f>SUM([3]調定07!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="H20" s="6">
-        <f>SUM([2]調定08!$G$4:$G$999)</f>
+        <f>SUM([3]調定08!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <f>SUM([2]調定09!$G$4:$G$999)</f>
+        <f>SUM([3]調定09!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="J20" s="6">
-        <f>SUM([2]調定10!$G$4:$G$999)</f>
+        <f>SUM([3]調定10!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <f>SUM([2]調定11!$G$4:$G$999)</f>
+        <f>SUM([3]調定11!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="L20" s="6">
-        <f>SUM([2]調定12!$G$4:$G$999)</f>
+        <f>SUM([3]調定12!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="M20" s="6">
-        <f>SUM([2]調定01!$G$4:$G$999)</f>
+        <f>SUM([3]調定01!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="N20" s="6">
-        <f>SUM([2]調定02!$G$4:$G$999)</f>
+        <f>SUM([3]調定02!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="O20" s="6">
-        <f>SUM([2]調定03!$G$4:$G$999)</f>
+        <f>SUM([3]調定03!$G$4:$G$999)</f>
         <v>0</v>
       </c>
       <c r="P20" s="6">
@@ -20778,14 +20778,14 @@
       <c r="M22" s="9"/>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="20" t="str">
-        <f>"令和"&amp;'[4]A-1'!$E$9-2018&amp;"年度  家電リサイクル収集運搬手数料"</f>
+      <c r="A23" s="15" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度  家電リサイクル収集運搬手数料"</f>
         <v>令和9年度  家電リサイクル収集運搬手数料</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="M23" s="9"/>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -20835,7 +20835,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="21" t="s">
         <v>16</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -20845,87 +20845,87 @@
         <v>3000</v>
       </c>
       <c r="D25" s="6">
-        <f>SUM([3]調定04!$I$24)
-+SUM([3]調定04!$I$48)
-+SUM([3]調定04!$I$72)
-+SUM([3]調定04!$I$96)</f>
+        <f>SUM([4]調定04!$I$24)
++SUM([4]調定04!$I$48)
++SUM([4]調定04!$I$72)
++SUM([4]調定04!$I$96)</f>
         <v>0</v>
       </c>
       <c r="E25" s="6">
-        <f>SUM([3]調定05!$I$24)
-+SUM([3]調定05!$I$48)
-+SUM([3]調定05!$I$72)
-+SUM([3]調定05!$I$96)</f>
+        <f>SUM([4]調定05!$I$24)
++SUM([4]調定05!$I$48)
++SUM([4]調定05!$I$72)
++SUM([4]調定05!$I$96)</f>
         <v>0</v>
       </c>
       <c r="F25" s="6">
-        <f>SUM([3]調定06!$I$24)
-+SUM([3]調定06!$I$48)
-+SUM([3]調定06!$I$72)
-+SUM([3]調定06!$I$96)</f>
+        <f>SUM([4]調定06!$I$24)
++SUM([4]調定06!$I$48)
++SUM([4]調定06!$I$72)
++SUM([4]調定06!$I$96)</f>
         <v>0</v>
       </c>
       <c r="G25" s="6">
-        <f>SUM([3]調定07!$I$24)
-+SUM([3]調定07!$I$48)
-+SUM([3]調定07!$I$72)
-+SUM([3]調定07!$I$96)</f>
+        <f>SUM([4]調定07!$I$24)
++SUM([4]調定07!$I$48)
++SUM([4]調定07!$I$72)
++SUM([4]調定07!$I$96)</f>
         <v>0</v>
       </c>
       <c r="H25" s="6">
-        <f>SUM([3]調定08!$I$24)
-+SUM([3]調定08!$I$48)
-+SUM([3]調定08!$I$72)
-+SUM([3]調定08!$I$96)</f>
+        <f>SUM([4]調定08!$I$24)
++SUM([4]調定08!$I$48)
++SUM([4]調定08!$I$72)
++SUM([4]調定08!$I$96)</f>
         <v>0</v>
       </c>
       <c r="I25" s="6">
-        <f>SUM([3]調定09!$I$24)
-+SUM([3]調定09!$I$48)
-+SUM([3]調定09!$I$72)
-+SUM([3]調定09!$I$96)</f>
+        <f>SUM([4]調定09!$I$24)
++SUM([4]調定09!$I$48)
++SUM([4]調定09!$I$72)
++SUM([4]調定09!$I$96)</f>
         <v>0</v>
       </c>
       <c r="J25" s="6">
-        <f>SUM([3]調定10!$I$24)
-+SUM([3]調定10!$I$48)
-+SUM([3]調定10!$I$72)
-+SUM([3]調定10!$I$96)</f>
+        <f>SUM([4]調定10!$I$24)
++SUM([4]調定10!$I$48)
++SUM([4]調定10!$I$72)
++SUM([4]調定10!$I$96)</f>
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <f>SUM([3]調定11!$I$24)
-+SUM([3]調定11!$I$48)
-+SUM([3]調定11!$I$72)
-+SUM([3]調定11!$I$96)</f>
+        <f>SUM([4]調定11!$I$24)
++SUM([4]調定11!$I$48)
++SUM([4]調定11!$I$72)
++SUM([4]調定11!$I$96)</f>
         <v>0</v>
       </c>
       <c r="L25" s="6">
-        <f>SUM([3]調定12!$I$24)
-+SUM([3]調定12!$I$48)
-+SUM([3]調定12!$I$72)
-+SUM([3]調定12!$I$96)</f>
+        <f>SUM([4]調定12!$I$24)
++SUM([4]調定12!$I$48)
++SUM([4]調定12!$I$72)
++SUM([4]調定12!$I$96)</f>
         <v>0</v>
       </c>
       <c r="M25" s="6">
-        <f>SUM([3]調定01!$I$24)
-+SUM([3]調定01!$I$48)
-+SUM([3]調定01!$I$72)
-+SUM([3]調定01!$I$96)</f>
+        <f>SUM([4]調定01!$I$24)
++SUM([4]調定01!$I$48)
++SUM([4]調定01!$I$72)
++SUM([4]調定01!$I$96)</f>
         <v>0</v>
       </c>
       <c r="N25" s="6">
-        <f>SUM([3]調定02!$I$24)
-+SUM([3]調定02!$I$48)
-+SUM([3]調定02!$I$72)
-+SUM([3]調定02!$I$96)</f>
+        <f>SUM([4]調定02!$I$24)
++SUM([4]調定02!$I$48)
++SUM([4]調定02!$I$72)
++SUM([4]調定02!$I$96)</f>
         <v>0</v>
       </c>
       <c r="O25" s="6">
-        <f>SUM([3]調定03!$I$24)
-+SUM([3]調定03!$I$48)
-+SUM([3]調定03!$I$72)
-+SUM([3]調定03!$I$96)</f>
+        <f>SUM([4]調定03!$I$24)
++SUM([4]調定03!$I$48)
++SUM([4]調定03!$I$72)
++SUM([4]調定03!$I$96)</f>
         <v>0</v>
       </c>
       <c r="P25" s="6">
@@ -20934,7 +20934,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="18"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="4" t="s">
         <v>23</v>
       </c>
@@ -20942,87 +20942,87 @@
         <v>3000</v>
       </c>
       <c r="D26" s="6">
-        <f>SUM([3]調定04!$K$24)
-+SUM([3]調定04!$K$48)
-+SUM([3]調定04!$K$72)
-+SUM([3]調定04!$K$96)</f>
+        <f>SUM([4]調定04!$K$24)
++SUM([4]調定04!$K$48)
++SUM([4]調定04!$K$72)
++SUM([4]調定04!$K$96)</f>
         <v>0</v>
       </c>
       <c r="E26" s="6">
-        <f>SUM([3]調定05!$K$24)
-+SUM([3]調定05!$K$48)
-+SUM([3]調定05!$K$72)
-+SUM([3]調定05!$K$96)</f>
+        <f>SUM([4]調定05!$K$24)
++SUM([4]調定05!$K$48)
++SUM([4]調定05!$K$72)
++SUM([4]調定05!$K$96)</f>
         <v>0</v>
       </c>
       <c r="F26" s="6">
-        <f>SUM([3]調定06!$K$24)
-+SUM([3]調定06!$K$48)
-+SUM([3]調定06!$K$72)
-+SUM([3]調定06!$K$96)</f>
+        <f>SUM([4]調定06!$K$24)
++SUM([4]調定06!$K$48)
++SUM([4]調定06!$K$72)
++SUM([4]調定06!$K$96)</f>
         <v>0</v>
       </c>
       <c r="G26" s="6">
-        <f>SUM([3]調定07!$K$24)
-+SUM([3]調定07!$K$48)
-+SUM([3]調定07!$K$72)
-+SUM([3]調定07!$K$96)</f>
+        <f>SUM([4]調定07!$K$24)
++SUM([4]調定07!$K$48)
++SUM([4]調定07!$K$72)
++SUM([4]調定07!$K$96)</f>
         <v>0</v>
       </c>
       <c r="H26" s="6">
-        <f>SUM([3]調定08!$K$24)
-+SUM([3]調定08!$K$48)
-+SUM([3]調定08!$K$72)
-+SUM([3]調定08!$K$96)</f>
+        <f>SUM([4]調定08!$K$24)
++SUM([4]調定08!$K$48)
++SUM([4]調定08!$K$72)
++SUM([4]調定08!$K$96)</f>
         <v>0</v>
       </c>
       <c r="I26" s="6">
-        <f>SUM([3]調定09!$K$24)
-+SUM([3]調定09!$K$48)
-+SUM([3]調定09!$K$72)
-+SUM([3]調定09!$K$96)</f>
+        <f>SUM([4]調定09!$K$24)
++SUM([4]調定09!$K$48)
++SUM([4]調定09!$K$72)
++SUM([4]調定09!$K$96)</f>
         <v>0</v>
       </c>
       <c r="J26" s="6">
-        <f>SUM([3]調定10!$K$24)
-+SUM([3]調定10!$K$48)
-+SUM([3]調定10!$K$72)
-+SUM([3]調定10!$K$96)</f>
+        <f>SUM([4]調定10!$K$24)
++SUM([4]調定10!$K$48)
++SUM([4]調定10!$K$72)
++SUM([4]調定10!$K$96)</f>
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <f>SUM([3]調定11!$K$24)
-+SUM([3]調定11!$K$48)
-+SUM([3]調定11!$K$72)
-+SUM([3]調定11!$K$96)</f>
+        <f>SUM([4]調定11!$K$24)
++SUM([4]調定11!$K$48)
++SUM([4]調定11!$K$72)
++SUM([4]調定11!$K$96)</f>
         <v>0</v>
       </c>
       <c r="L26" s="6">
-        <f>SUM([3]調定12!$K$24)
-+SUM([3]調定12!$K$48)
-+SUM([3]調定12!$K$72)
-+SUM([3]調定12!$K$96)</f>
+        <f>SUM([4]調定12!$K$24)
++SUM([4]調定12!$K$48)
++SUM([4]調定12!$K$72)
++SUM([4]調定12!$K$96)</f>
         <v>0</v>
       </c>
       <c r="M26" s="6">
-        <f>SUM([3]調定01!$K$24)
-+SUM([3]調定01!$K$48)
-+SUM([3]調定01!$K$72)
-+SUM([3]調定01!$K$96)</f>
+        <f>SUM([4]調定01!$K$24)
++SUM([4]調定01!$K$48)
++SUM([4]調定01!$K$72)
++SUM([4]調定01!$K$96)</f>
         <v>0</v>
       </c>
       <c r="N26" s="6">
-        <f>SUM([3]調定02!$K$24)
-+SUM([3]調定02!$K$48)
-+SUM([3]調定02!$K$72)
-+SUM([3]調定02!$K$96)</f>
+        <f>SUM([4]調定02!$K$24)
++SUM([4]調定02!$K$48)
++SUM([4]調定02!$K$72)
++SUM([4]調定02!$K$96)</f>
         <v>0</v>
       </c>
       <c r="O26" s="6">
-        <f>SUM([3]調定03!$K$24)
-+SUM([3]調定03!$K$48)
-+SUM([3]調定03!$K$72)
-+SUM([3]調定03!$K$96)</f>
+        <f>SUM([4]調定03!$K$24)
++SUM([4]調定03!$K$48)
++SUM([4]調定03!$K$72)
++SUM([4]調定03!$K$96)</f>
         <v>0</v>
       </c>
       <c r="P26" s="6">
@@ -21031,7 +21031,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="18"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="4" t="s">
         <v>27</v>
       </c>
@@ -21039,87 +21039,87 @@
         <v>3000</v>
       </c>
       <c r="D27" s="6">
-        <f>SUM([3]調定04!$G$24)
-+SUM([3]調定04!$G$48)
-+SUM([3]調定04!$G$72)
-+SUM([3]調定04!$G$96)</f>
+        <f>SUM([4]調定04!$G$24)
++SUM([4]調定04!$G$48)
++SUM([4]調定04!$G$72)
++SUM([4]調定04!$G$96)</f>
         <v>0</v>
       </c>
       <c r="E27" s="6">
-        <f>SUM([3]調定05!$G$24)
-+SUM([3]調定05!$G$48)
-+SUM([3]調定05!$G$72)
-+SUM([3]調定05!$G$96)</f>
+        <f>SUM([4]調定05!$G$24)
++SUM([4]調定05!$G$48)
++SUM([4]調定05!$G$72)
++SUM([4]調定05!$G$96)</f>
         <v>0</v>
       </c>
       <c r="F27" s="6">
-        <f>SUM([3]調定06!$G$24)
-+SUM([3]調定06!$G$48)
-+SUM([3]調定06!$G$72)
-+SUM([3]調定06!$G$96)</f>
+        <f>SUM([4]調定06!$G$24)
++SUM([4]調定06!$G$48)
++SUM([4]調定06!$G$72)
++SUM([4]調定06!$G$96)</f>
         <v>0</v>
       </c>
       <c r="G27" s="6">
-        <f>SUM([3]調定07!$G$24)
-+SUM([3]調定07!$G$48)
-+SUM([3]調定07!$G$72)
-+SUM([3]調定07!$G$96)</f>
+        <f>SUM([4]調定07!$G$24)
++SUM([4]調定07!$G$48)
++SUM([4]調定07!$G$72)
++SUM([4]調定07!$G$96)</f>
         <v>0</v>
       </c>
       <c r="H27" s="6">
-        <f>SUM([3]調定08!$G$24)
-+SUM([3]調定08!$G$48)
-+SUM([3]調定08!$G$72)
-+SUM([3]調定08!$G$96)</f>
+        <f>SUM([4]調定08!$G$24)
++SUM([4]調定08!$G$48)
++SUM([4]調定08!$G$72)
++SUM([4]調定08!$G$96)</f>
         <v>0</v>
       </c>
       <c r="I27" s="6">
-        <f>SUM([3]調定09!$G$24)
-+SUM([3]調定09!$G$48)
-+SUM([3]調定09!$G$72)
-+SUM([3]調定09!$G$96)</f>
+        <f>SUM([4]調定09!$G$24)
++SUM([4]調定09!$G$48)
++SUM([4]調定09!$G$72)
++SUM([4]調定09!$G$96)</f>
         <v>0</v>
       </c>
       <c r="J27" s="6">
-        <f>SUM([3]調定10!$G$24)
-+SUM([3]調定10!$G$48)
-+SUM([3]調定10!$G$72)
-+SUM([3]調定10!$G$96)</f>
+        <f>SUM([4]調定10!$G$24)
++SUM([4]調定10!$G$48)
++SUM([4]調定10!$G$72)
++SUM([4]調定10!$G$96)</f>
         <v>0</v>
       </c>
       <c r="K27" s="6">
-        <f>SUM([3]調定11!$G$24)
-+SUM([3]調定11!$G$48)
-+SUM([3]調定11!$G$72)
-+SUM([3]調定11!$G$96)</f>
+        <f>SUM([4]調定11!$G$24)
++SUM([4]調定11!$G$48)
++SUM([4]調定11!$G$72)
++SUM([4]調定11!$G$96)</f>
         <v>0</v>
       </c>
       <c r="L27" s="6">
-        <f>SUM([3]調定12!$G$24)
-+SUM([3]調定12!$G$48)
-+SUM([3]調定12!$G$72)
-+SUM([3]調定12!$G$96)</f>
+        <f>SUM([4]調定12!$G$24)
++SUM([4]調定12!$G$48)
++SUM([4]調定12!$G$72)
++SUM([4]調定12!$G$96)</f>
         <v>0</v>
       </c>
       <c r="M27" s="6">
-        <f>SUM([3]調定01!$G$24)
-+SUM([3]調定01!$G$48)
-+SUM([3]調定01!$G$72)
-+SUM([3]調定01!$G$96)</f>
+        <f>SUM([4]調定01!$G$24)
++SUM([4]調定01!$G$48)
++SUM([4]調定01!$G$72)
++SUM([4]調定01!$G$96)</f>
         <v>0</v>
       </c>
       <c r="N27" s="6">
-        <f>SUM([3]調定02!$G$24)
-+SUM([3]調定02!$G$48)
-+SUM([3]調定02!$G$72)
-+SUM([3]調定02!$G$96)</f>
+        <f>SUM([4]調定02!$G$24)
++SUM([4]調定02!$G$48)
++SUM([4]調定02!$G$72)
++SUM([4]調定02!$G$96)</f>
         <v>0</v>
       </c>
       <c r="O27" s="6">
-        <f>SUM([3]調定03!$G$24)
-+SUM([3]調定03!$G$48)
-+SUM([3]調定03!$G$72)
-+SUM([3]調定03!$G$96)</f>
+        <f>SUM([4]調定03!$G$24)
++SUM([4]調定03!$G$48)
++SUM([4]調定03!$G$72)
++SUM([4]調定03!$G$96)</f>
         <v>0</v>
       </c>
       <c r="P27" s="6">
@@ -21128,7 +21128,7 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="18"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
@@ -21136,87 +21136,87 @@
         <v>2000</v>
       </c>
       <c r="D28" s="6">
-        <f>SUM([3]調定04!$M$24)
-+SUM([3]調定04!$M$48)
-+SUM([3]調定04!$M$72)
-+SUM([3]調定04!$M$96)</f>
+        <f>SUM([4]調定04!$M$24)
++SUM([4]調定04!$M$48)
++SUM([4]調定04!$M$72)
++SUM([4]調定04!$M$96)</f>
         <v>0</v>
       </c>
       <c r="E28" s="6">
-        <f>SUM([3]調定05!$M$24)
-+SUM([3]調定05!$M$48)
-+SUM([3]調定05!$M$72)
-+SUM([3]調定05!$M$96)</f>
+        <f>SUM([4]調定05!$M$24)
++SUM([4]調定05!$M$48)
++SUM([4]調定05!$M$72)
++SUM([4]調定05!$M$96)</f>
         <v>0</v>
       </c>
       <c r="F28" s="6">
-        <f>SUM([3]調定06!$M$24)
-+SUM([3]調定06!$M$48)
-+SUM([3]調定06!$M$72)
-+SUM([3]調定06!$M$96)</f>
+        <f>SUM([4]調定06!$M$24)
++SUM([4]調定06!$M$48)
++SUM([4]調定06!$M$72)
++SUM([4]調定06!$M$96)</f>
         <v>0</v>
       </c>
       <c r="G28" s="6">
-        <f>SUM([3]調定07!$M$24)
-+SUM([3]調定07!$M$48)
-+SUM([3]調定07!$M$72)
-+SUM([3]調定07!$M$96)</f>
+        <f>SUM([4]調定07!$M$24)
++SUM([4]調定07!$M$48)
++SUM([4]調定07!$M$72)
++SUM([4]調定07!$M$96)</f>
         <v>0</v>
       </c>
       <c r="H28" s="6">
-        <f>SUM([3]調定08!$M$24)
-+SUM([3]調定08!$M$48)
-+SUM([3]調定08!$M$72)
-+SUM([3]調定08!$M$96)</f>
+        <f>SUM([4]調定08!$M$24)
++SUM([4]調定08!$M$48)
++SUM([4]調定08!$M$72)
++SUM([4]調定08!$M$96)</f>
         <v>0</v>
       </c>
       <c r="I28" s="6">
-        <f>SUM([3]調定09!$M$24)
-+SUM([3]調定09!$M$48)
-+SUM([3]調定09!$M$72)
-+SUM([3]調定09!$M$96)</f>
+        <f>SUM([4]調定09!$M$24)
++SUM([4]調定09!$M$48)
++SUM([4]調定09!$M$72)
++SUM([4]調定09!$M$96)</f>
         <v>0</v>
       </c>
       <c r="J28" s="6">
-        <f>SUM([3]調定10!$M$24)
-+SUM([3]調定10!$M$48)
-+SUM([3]調定10!$M$72)
-+SUM([3]調定10!$M$96)</f>
+        <f>SUM([4]調定10!$M$24)
++SUM([4]調定10!$M$48)
++SUM([4]調定10!$M$72)
++SUM([4]調定10!$M$96)</f>
         <v>0</v>
       </c>
       <c r="K28" s="6">
-        <f>SUM([3]調定11!$M$24)
-+SUM([3]調定11!$M$48)
-+SUM([3]調定11!$M$72)
-+SUM([3]調定11!$M$96)</f>
+        <f>SUM([4]調定11!$M$24)
++SUM([4]調定11!$M$48)
++SUM([4]調定11!$M$72)
++SUM([4]調定11!$M$96)</f>
         <v>0</v>
       </c>
       <c r="L28" s="6">
-        <f>SUM([3]調定12!$M$24)
-+SUM([3]調定12!$M$48)
-+SUM([3]調定12!$M$72)
-+SUM([3]調定12!$M$96)</f>
+        <f>SUM([4]調定12!$M$24)
++SUM([4]調定12!$M$48)
++SUM([4]調定12!$M$72)
++SUM([4]調定12!$M$96)</f>
         <v>0</v>
       </c>
       <c r="M28" s="6">
-        <f>SUM([3]調定01!$M$24)
-+SUM([3]調定01!$M$48)
-+SUM([3]調定01!$M$72)
-+SUM([3]調定01!$M$96)</f>
+        <f>SUM([4]調定01!$M$24)
++SUM([4]調定01!$M$48)
++SUM([4]調定01!$M$72)
++SUM([4]調定01!$M$96)</f>
         <v>0</v>
       </c>
       <c r="N28" s="6">
-        <f>SUM([3]調定02!$M$24)
-+SUM([3]調定02!$M$48)
-+SUM([3]調定02!$M$72)
-+SUM([3]調定02!$M$96)</f>
+        <f>SUM([4]調定02!$M$24)
++SUM([4]調定02!$M$48)
++SUM([4]調定02!$M$72)
++SUM([4]調定02!$M$96)</f>
         <v>0</v>
       </c>
       <c r="O28" s="6">
-        <f>SUM([3]調定03!$M$24)
-+SUM([3]調定03!$M$48)
-+SUM([3]調定03!$M$72)
-+SUM([3]調定03!$M$96)</f>
+        <f>SUM([4]調定03!$M$24)
++SUM([4]調定03!$M$48)
++SUM([4]調定03!$M$72)
++SUM([4]調定03!$M$96)</f>
         <v>0</v>
       </c>
       <c r="P28" s="6">
@@ -21225,7 +21225,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="18"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="4" t="s">
         <v>25</v>
       </c>
@@ -21233,87 +21233,87 @@
         <v>2000</v>
       </c>
       <c r="D29" s="6">
-        <f>SUM([3]調定04!$O$24)
-+SUM([3]調定04!$O$48)
-+SUM([3]調定04!$O$72)
-+SUM([3]調定04!$O$96)</f>
+        <f>SUM([4]調定04!$O$24)
++SUM([4]調定04!$O$48)
++SUM([4]調定04!$O$72)
++SUM([4]調定04!$O$96)</f>
         <v>0</v>
       </c>
       <c r="E29" s="6">
-        <f>SUM([3]調定05!$O$24)
-+SUM([3]調定05!$O$48)
-+SUM([3]調定05!$O$72)
-+SUM([3]調定05!$O$96)</f>
+        <f>SUM([4]調定05!$O$24)
++SUM([4]調定05!$O$48)
++SUM([4]調定05!$O$72)
++SUM([4]調定05!$O$96)</f>
         <v>0</v>
       </c>
       <c r="F29" s="6">
-        <f>SUM([3]調定06!$O$24)
-+SUM([3]調定06!$O$48)
-+SUM([3]調定06!$O$72)
-+SUM([3]調定06!$O$96)</f>
+        <f>SUM([4]調定06!$O$24)
++SUM([4]調定06!$O$48)
++SUM([4]調定06!$O$72)
++SUM([4]調定06!$O$96)</f>
         <v>0</v>
       </c>
       <c r="G29" s="6">
-        <f>SUM([3]調定07!$O$24)
-+SUM([3]調定07!$O$48)
-+SUM([3]調定07!$O$72)
-+SUM([3]調定07!$O$96)</f>
+        <f>SUM([4]調定07!$O$24)
++SUM([4]調定07!$O$48)
++SUM([4]調定07!$O$72)
++SUM([4]調定07!$O$96)</f>
         <v>0</v>
       </c>
       <c r="H29" s="6">
-        <f>SUM([3]調定08!$O$24)
-+SUM([3]調定08!$O$48)
-+SUM([3]調定08!$O$72)
-+SUM([3]調定08!$O$96)</f>
+        <f>SUM([4]調定08!$O$24)
++SUM([4]調定08!$O$48)
++SUM([4]調定08!$O$72)
++SUM([4]調定08!$O$96)</f>
         <v>0</v>
       </c>
       <c r="I29" s="6">
-        <f>SUM([3]調定09!$O$24)
-+SUM([3]調定09!$O$48)
-+SUM([3]調定09!$O$72)
-+SUM([3]調定09!$O$96)</f>
+        <f>SUM([4]調定09!$O$24)
++SUM([4]調定09!$O$48)
++SUM([4]調定09!$O$72)
++SUM([4]調定09!$O$96)</f>
         <v>0</v>
       </c>
       <c r="J29" s="6">
-        <f>SUM([3]調定10!$O$24)
-+SUM([3]調定10!$O$48)
-+SUM([3]調定10!$O$72)
-+SUM([3]調定10!$O$96)</f>
+        <f>SUM([4]調定10!$O$24)
++SUM([4]調定10!$O$48)
++SUM([4]調定10!$O$72)
++SUM([4]調定10!$O$96)</f>
         <v>0</v>
       </c>
       <c r="K29" s="6">
-        <f>SUM([3]調定11!$O$24)
-+SUM([3]調定11!$O$48)
-+SUM([3]調定11!$O$72)
-+SUM([3]調定11!$O$96)</f>
+        <f>SUM([4]調定11!$O$24)
++SUM([4]調定11!$O$48)
++SUM([4]調定11!$O$72)
++SUM([4]調定11!$O$96)</f>
         <v>0</v>
       </c>
       <c r="L29" s="6">
-        <f>SUM([3]調定12!$O$24)
-+SUM([3]調定12!$O$48)
-+SUM([3]調定12!$O$72)
-+SUM([3]調定12!$O$96)</f>
+        <f>SUM([4]調定12!$O$24)
++SUM([4]調定12!$O$48)
++SUM([4]調定12!$O$72)
++SUM([4]調定12!$O$96)</f>
         <v>0</v>
       </c>
       <c r="M29" s="6">
-        <f>SUM([3]調定01!$O$24)
-+SUM([3]調定01!$O$48)
-+SUM([3]調定01!$O$72)
-+SUM([3]調定01!$O$96)</f>
+        <f>SUM([4]調定01!$O$24)
++SUM([4]調定01!$O$48)
++SUM([4]調定01!$O$72)
++SUM([4]調定01!$O$96)</f>
         <v>0</v>
       </c>
       <c r="N29" s="6">
-        <f>SUM([3]調定02!$O$24)
-+SUM([3]調定02!$O$48)
-+SUM([3]調定02!$O$72)
-+SUM([3]調定02!$O$96)</f>
+        <f>SUM([4]調定02!$O$24)
++SUM([4]調定02!$O$48)
++SUM([4]調定02!$O$72)
++SUM([4]調定02!$O$96)</f>
         <v>0</v>
       </c>
       <c r="O29" s="6">
-        <f>SUM([3]調定03!$O$24)
-+SUM([3]調定03!$O$48)
-+SUM([3]調定03!$O$72)
-+SUM([3]調定03!$O$96)</f>
+        <f>SUM([4]調定03!$O$24)
++SUM([4]調定03!$O$48)
++SUM([4]調定03!$O$72)
++SUM([4]調定03!$O$96)</f>
         <v>0</v>
       </c>
       <c r="P29" s="6">
@@ -21322,7 +21322,7 @@
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="15"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="4" t="s">
         <v>28</v>
       </c>
@@ -21330,87 +21330,87 @@
         <v>2000</v>
       </c>
       <c r="D30" s="6">
-        <f>SUM([3]調定04!$E$24)
-+SUM([3]調定04!$E$48)
-+SUM([3]調定04!$E$72)
-+SUM([3]調定04!$E$96)</f>
+        <f>SUM([4]調定04!$E$24)
++SUM([4]調定04!$E$48)
++SUM([4]調定04!$E$72)
++SUM([4]調定04!$E$96)</f>
         <v>0</v>
       </c>
       <c r="E30" s="6">
-        <f>SUM([3]調定05!$E$24)
-+SUM([3]調定05!$E$48)
-+SUM([3]調定05!$E$72)
-+SUM([3]調定05!$E$96)</f>
+        <f>SUM([4]調定05!$E$24)
++SUM([4]調定05!$E$48)
++SUM([4]調定05!$E$72)
++SUM([4]調定05!$E$96)</f>
         <v>0</v>
       </c>
       <c r="F30" s="6">
-        <f>SUM([3]調定06!$E$24)
-+SUM([3]調定06!$E$48)
-+SUM([3]調定06!$E$72)
-+SUM([3]調定06!$E$96)</f>
+        <f>SUM([4]調定06!$E$24)
++SUM([4]調定06!$E$48)
++SUM([4]調定06!$E$72)
++SUM([4]調定06!$E$96)</f>
         <v>0</v>
       </c>
       <c r="G30" s="6">
-        <f>SUM([3]調定07!$E$24)
-+SUM([3]調定07!$E$48)
-+SUM([3]調定07!$E$72)
-+SUM([3]調定07!$E$96)</f>
+        <f>SUM([4]調定07!$E$24)
++SUM([4]調定07!$E$48)
++SUM([4]調定07!$E$72)
++SUM([4]調定07!$E$96)</f>
         <v>0</v>
       </c>
       <c r="H30" s="6">
-        <f>SUM([3]調定08!$E$24)
-+SUM([3]調定08!$E$48)
-+SUM([3]調定08!$E$72)
-+SUM([3]調定08!$E$96)</f>
+        <f>SUM([4]調定08!$E$24)
++SUM([4]調定08!$E$48)
++SUM([4]調定08!$E$72)
++SUM([4]調定08!$E$96)</f>
         <v>0</v>
       </c>
       <c r="I30" s="6">
-        <f>SUM([3]調定09!$E$24)
-+SUM([3]調定09!$E$48)
-+SUM([3]調定09!$E$72)
-+SUM([3]調定09!$E$96)</f>
+        <f>SUM([4]調定09!$E$24)
++SUM([4]調定09!$E$48)
++SUM([4]調定09!$E$72)
++SUM([4]調定09!$E$96)</f>
         <v>0</v>
       </c>
       <c r="J30" s="6">
-        <f>SUM([3]調定10!$E$24)
-+SUM([3]調定10!$E$48)
-+SUM([3]調定10!$E$72)
-+SUM([3]調定10!$E$96)</f>
+        <f>SUM([4]調定10!$E$24)
++SUM([4]調定10!$E$48)
++SUM([4]調定10!$E$72)
++SUM([4]調定10!$E$96)</f>
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <f>SUM([3]調定11!$E$24)
-+SUM([3]調定11!$E$48)
-+SUM([3]調定11!$E$72)
-+SUM([3]調定11!$E$96)</f>
+        <f>SUM([4]調定11!$E$24)
++SUM([4]調定11!$E$48)
++SUM([4]調定11!$E$72)
++SUM([4]調定11!$E$96)</f>
         <v>0</v>
       </c>
       <c r="L30" s="6">
-        <f>SUM([3]調定12!$E$24)
-+SUM([3]調定12!$E$48)
-+SUM([3]調定12!$E$72)
-+SUM([3]調定12!$E$96)</f>
+        <f>SUM([4]調定12!$E$24)
++SUM([4]調定12!$E$48)
++SUM([4]調定12!$E$72)
++SUM([4]調定12!$E$96)</f>
         <v>0</v>
       </c>
       <c r="M30" s="6">
-        <f>SUM([3]調定01!$E$24)
-+SUM([3]調定01!$E$48)
-+SUM([3]調定01!$E$72)
-+SUM([3]調定01!$E$96)</f>
+        <f>SUM([4]調定01!$E$24)
++SUM([4]調定01!$E$48)
++SUM([4]調定01!$E$72)
++SUM([4]調定01!$E$96)</f>
         <v>0</v>
       </c>
       <c r="N30" s="6">
-        <f>SUM([3]調定02!$E$24)
-+SUM([3]調定02!$E$48)
-+SUM([3]調定02!$E$72)
-+SUM([3]調定02!$E$96)</f>
+        <f>SUM([4]調定02!$E$24)
++SUM([4]調定02!$E$48)
++SUM([4]調定02!$E$72)
++SUM([4]調定02!$E$96)</f>
         <v>0</v>
       </c>
       <c r="O30" s="6">
-        <f>SUM([3]調定03!$E$24)
-+SUM([3]調定03!$E$48)
-+SUM([3]調定03!$E$72)
-+SUM([3]調定03!$E$96)</f>
+        <f>SUM([4]調定03!$E$24)
++SUM([4]調定03!$E$48)
++SUM([4]調定03!$E$72)
++SUM([4]調定03!$E$96)</f>
         <v>0</v>
       </c>
       <c r="P30" s="6">
@@ -21419,22 +21419,22 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="23"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="19"/>
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="16" t="s">
@@ -21805,11 +21805,11 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
       <c r="D38" s="10">
         <f>SUM(D32:D37)</f>
         <v>0</v>
@@ -21864,11 +21864,11 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="13" t="str">
         <f>IF(SUM(D10,D21,D38)=0,"",SUM(D10,D21,D38))</f>
         <v/>
@@ -21924,14 +21924,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="A31:P31"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A7:A9"/>
@@ -21943,6 +21935,14 @@
     <mergeCell ref="A25:A30"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
